--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N115_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N115_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.24561177802004</v>
+        <v>8.489911913928257</v>
       </c>
       <c r="D2" t="n">
-        <v>51.94710961940905</v>
+        <v>8.441405313153972</v>
       </c>
       <c r="E2" t="n">
-        <v>10.29781274656239</v>
+        <v>1.673394571316389</v>
       </c>
       <c r="F2" t="n">
-        <v>13.36427263344197</v>
+        <v>2.171694302934319</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.9823438382598</v>
+        <v>5.197130873717217</v>
       </c>
       <c r="D3" t="n">
-        <v>31.75373470382398</v>
+        <v>5.159981889371396</v>
       </c>
       <c r="E3" t="n">
-        <v>10.29781274656239</v>
+        <v>1.673394571316389</v>
       </c>
       <c r="F3" t="n">
-        <v>13.36427263344197</v>
+        <v>2.171694302934319</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.62107639395396</v>
+        <v>6.275924914017519</v>
       </c>
       <c r="D4" t="n">
-        <v>33.88613887953694</v>
+        <v>5.506497567924754</v>
       </c>
       <c r="E4" t="n">
-        <v>10.29781274656239</v>
+        <v>1.673394571316389</v>
       </c>
       <c r="F4" t="n">
-        <v>13.36427263344197</v>
+        <v>2.171694302934319</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.31480614585364</v>
+        <v>3.301155998701216</v>
       </c>
       <c r="D5" t="n">
-        <v>16.52542788733652</v>
+        <v>2.685382031692185</v>
       </c>
       <c r="E5" t="n">
-        <v>10.29781274656239</v>
+        <v>1.673394571316389</v>
       </c>
       <c r="F5" t="n">
-        <v>13.36427263344197</v>
+        <v>2.171694302934319</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.49663224652901</v>
+        <v>8.205702740060964</v>
       </c>
       <c r="D6" t="n">
-        <v>45.42898270651944</v>
+        <v>7.382209689809409</v>
       </c>
       <c r="E6" t="n">
-        <v>10.29781274656239</v>
+        <v>1.673394571316389</v>
       </c>
       <c r="F6" t="n">
-        <v>13.36427263344197</v>
+        <v>2.171694302934319</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.39868197939274</v>
+        <v>6.564785821651321</v>
       </c>
       <c r="D7" t="n">
-        <v>16.1578277816605</v>
+        <v>2.625647014519831</v>
       </c>
       <c r="E7" t="n">
-        <v>10.29781274656239</v>
+        <v>1.673394571316389</v>
       </c>
       <c r="F7" t="n">
-        <v>13.36427263344197</v>
+        <v>2.171694302934319</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.32766399296278</v>
+        <v>7.365745398856451</v>
       </c>
       <c r="D8" t="n">
-        <v>47.11706692106241</v>
+        <v>7.656523374672642</v>
       </c>
       <c r="E8" t="n">
-        <v>10.29781274656239</v>
+        <v>1.673394571316389</v>
       </c>
       <c r="F8" t="n">
-        <v>13.36427263344197</v>
+        <v>2.171694302934319</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
